--- a/public/quizdrop-template-trivia.xlsx
+++ b/public/quizdrop-template-trivia.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="48">
   <si>
     <t xml:space="preserve">QuizDrop — Trivia Upload Template</t>
   </si>
@@ -72,7 +72,7 @@
     <t xml:space="preserve">type</t>
   </si>
   <si>
-    <t xml:space="preserve">Required dropdown. One of: multiple_choice, true_false, fill_blank, short_answer</t>
+    <t xml:space="preserve">Required dropdown. One of: multiple_choice, true_false, short_answer</t>
   </si>
   <si>
     <t xml:space="preserve">text</t>
@@ -84,13 +84,13 @@
     <t xml:space="preserve">option1 – option8</t>
   </si>
   <si>
-    <t xml:space="preserve">Multiple choice / true-false only. Up to 8 answer choices. Leave blank for fill_blank and short_answer.</t>
+    <t xml:space="preserve">Multiple choice / true-false only. Up to 8 answer choices. Leave blank for short_answer.</t>
   </si>
   <si>
     <t xml:space="preserve">correct</t>
   </si>
   <si>
-    <t xml:space="preserve">Multiple choice: the option NUMBER that's correct (e.g. 1 for option1, 2 for option2). True/false: type True or False. Fill in the blank / short answer: list every acceptable answer, separated by commas (e.g. "Mars, mars planet").</t>
+    <t xml:space="preserve">Multiple choice: the option NUMBER that's correct (e.g. 1 for option1, 2 for option2). True/false: type True or False. Short answer: list every acceptable answer, separated by commas (e.g. "Mars, mars planet").</t>
   </si>
   <si>
     <t xml:space="preserve">time_limit</t>
@@ -120,16 +120,10 @@
     <t xml:space="preserve">A simple True or False question.</t>
   </si>
   <si>
-    <t xml:space="preserve">fill_blank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Players type a short answer. List every acceptable spelling/phrasing in "correct."</t>
-  </si>
-  <si>
     <t xml:space="preserve">short_answer</t>
   </si>
   <si>
-    <t xml:space="preserve">Same as fill in the blank, but for longer typed responses.</t>
+    <t xml:space="preserve">Players type their answer. List every acceptable spelling/phrasing in "correct."</t>
   </si>
   <si>
     <t xml:space="preserve">Tips</t>
@@ -623,7 +617,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -788,31 +782,29 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
     </row>
-    <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+    </row>
+    <row r="21" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -822,7 +814,7 @@
     </row>
     <row r="22" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -830,9 +822,9 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
     </row>
-    <row r="23" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -840,18 +832,8 @@
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-    </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="19">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A4:F4"/>
@@ -866,12 +848,11 @@
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A24:F24"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -908,28 +889,28 @@
         <v>6</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>35</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>37</v>
       </c>
       <c r="K1" s="6" t="s">
         <v>10</v>
@@ -946,22 +927,22 @@
         <v>17</v>
       </c>
       <c r="B2" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="E2" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="F2" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="K2" s="0" t="s">
         <v>41</v>
-      </c>
-      <c r="F2" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="K2" s="0" t="s">
-        <v>43</v>
       </c>
       <c r="L2" s="0" t="n">
         <v>45</v>
@@ -972,10 +953,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L3" s="0" t="n">
         <v>30</v>
@@ -986,10 +967,10 @@
         <v>21</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K4" s="0" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L4" s="0" t="n">
         <v>45</v>
@@ -997,13 +978,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L5" s="0" t="n">
         <v>60</v>
@@ -2497,7 +2478,7 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation allowBlank="false" error="Please choose a value from the dropdown list." errorStyle="stop" errorTitle="Invalid question type" operator="between" prompt="Choose a question type" promptTitle="Question type" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="A2:A500" type="list">
-      <formula1>"multiple_choice,true_false,fill_blank,short_answer"</formula1>
+      <formula1>"multiple_choice,true_false,short_answer"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Please choose a value from the dropdown list." errorStyle="stop" errorTitle="Invalid time limit" operator="between" prompt="Seconds allowed to answer (defaults to 45 if left blank)" promptTitle="Time limit" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L2:L500" type="list">
